--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga Emas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harga Emas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5033</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5035</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5033"/>
+  <dimension ref="A1:D5035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -64947,8 +64947,36 @@
         <v>147000</v>
       </c>
     </row>
+    <row r="5034">
+      <c r="A5034" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B5034" s="3" t="n">
+        <v>2624000</v>
+      </c>
+      <c r="C5034" s="3" t="n">
+        <v>2477000</v>
+      </c>
+      <c r="D5034" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
+    <row r="5035">
+      <c r="A5035" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B5035" s="3" t="n">
+        <v>2639000</v>
+      </c>
+      <c r="C5035" s="3" t="n">
+        <v>2492000</v>
+      </c>
+      <c r="D5035" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5033"/>
+  <autoFilter ref="A1:D5035"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -64998,7 +65026,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:20:29 WIB</t>
+          <t>2026-09-03 14:18:09 WIB</t>
         </is>
       </c>
     </row>
@@ -65009,7 +65037,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5032</v>
+        <v>5034</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5035</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5036</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5035"/>
+  <dimension ref="A1:D5036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -64975,8 +64975,22 @@
         <v>147000</v>
       </c>
     </row>
+    <row r="5036">
+      <c r="A5036" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B5036" s="3" t="n">
+        <v>2670000</v>
+      </c>
+      <c r="C5036" s="3" t="n">
+        <v>2523000</v>
+      </c>
+      <c r="D5036" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5035"/>
+  <autoFilter ref="A1:D5036"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65026,7 +65040,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:18:09 WIB</t>
+          <t>2026-09-04 14:25:52 WIB</t>
         </is>
       </c>
     </row>
@@ -65037,7 +65051,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5034</v>
+        <v>5035</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5036</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5037</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5036"/>
+  <dimension ref="A1:D5037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -64989,8 +64989,22 @@
         <v>147000</v>
       </c>
     </row>
+    <row r="5037">
+      <c r="A5037" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B5037" s="3" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="C5037" s="3" t="n">
+        <v>2493000</v>
+      </c>
+      <c r="D5037" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5036"/>
+  <autoFilter ref="A1:D5037"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65040,7 +65054,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04 14:25:52 WIB</t>
+          <t>2026-09-05 14:02:41 WIB</t>
         </is>
       </c>
     </row>
@@ -65051,7 +65065,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5035</v>
+        <v>5036</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5037</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5039</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5037"/>
+  <dimension ref="A1:D5039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65003,8 +65003,36 @@
         <v>147000</v>
       </c>
     </row>
+    <row r="5038">
+      <c r="A5038" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B5038" s="3" t="n">
+        <v>2640000</v>
+      </c>
+      <c r="C5038" s="3" t="n">
+        <v>2493000</v>
+      </c>
+      <c r="D5038" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
+    <row r="5039">
+      <c r="A5039" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B5039" s="3" t="n">
+        <v>2637000</v>
+      </c>
+      <c r="C5039" s="3" t="n">
+        <v>2490000</v>
+      </c>
+      <c r="D5039" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5037"/>
+  <autoFilter ref="A1:D5039"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65054,7 +65082,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-05 14:02:41 WIB</t>
+          <t>2026-09-07 14:27:11 WIB</t>
         </is>
       </c>
     </row>
@@ -65065,7 +65093,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5036</v>
+        <v>5038</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5039</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5040</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5039"/>
+  <dimension ref="A1:D5040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65031,8 +65031,22 @@
         <v>147000</v>
       </c>
     </row>
+    <row r="5040">
+      <c r="A5040" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B5040" s="3" t="n">
+        <v>2627000</v>
+      </c>
+      <c r="C5040" s="3" t="n">
+        <v>2480000</v>
+      </c>
+      <c r="D5040" s="3" t="n">
+        <v>147000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5039"/>
+  <autoFilter ref="A1:D5040"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65082,7 +65096,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 14:27:11 WIB</t>
+          <t>2026-09-08 14:21:12 WIB</t>
         </is>
       </c>
     </row>
@@ -65093,7 +65107,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5038</v>
+        <v>5039</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5040</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5041</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5040"/>
+  <dimension ref="A1:D5041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65045,8 +65045,22 @@
         <v>147000</v>
       </c>
     </row>
+    <row r="5041">
+      <c r="A5041" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B5041" s="3" t="n">
+        <v>2610000</v>
+      </c>
+      <c r="C5041" s="3" t="n">
+        <v>2460000</v>
+      </c>
+      <c r="D5041" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5040"/>
+  <autoFilter ref="A1:D5041"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65096,7 +65110,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:21:12 WIB</t>
+          <t>2026-09-09 14:29:38 WIB</t>
         </is>
       </c>
     </row>
@@ -65107,7 +65121,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5039</v>
+        <v>5040</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5042</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5041"/>
+  <dimension ref="A1:D5042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65059,8 +65059,22 @@
         <v>150000</v>
       </c>
     </row>
+    <row r="5042">
+      <c r="A5042" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B5042" s="3" t="n">
+        <v>2625000</v>
+      </c>
+      <c r="C5042" s="3" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="D5042" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5041"/>
+  <autoFilter ref="A1:D5042"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65110,7 +65124,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:29:38 WIB</t>
+          <t>2026-09-10 14:26:02 WIB</t>
         </is>
       </c>
     </row>
@@ -65121,7 +65135,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5040</v>
+        <v>5041</v>
       </c>
     </row>
   </sheetData>

--- a/data/harga_emas_antam.xlsx
+++ b/data/harga_emas_antam.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5042</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Harga Emas'!$A$1:$D$5044</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5042"/>
+  <dimension ref="A1:D5044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65073,8 +65073,36 @@
         <v>150000</v>
       </c>
     </row>
+    <row r="5043">
+      <c r="A5043" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B5043" s="3" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="C5043" s="3" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="D5043" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="5044">
+      <c r="A5044" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B5044" s="3" t="n">
+        <v>2604000</v>
+      </c>
+      <c r="C5044" s="3" t="n">
+        <v>2454000</v>
+      </c>
+      <c r="D5044" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5042"/>
+  <autoFilter ref="A1:D5044"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65124,7 +65152,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:26:02 WIB</t>
+          <t>2026-09-12 14:16:29 WIB</t>
         </is>
       </c>
     </row>
@@ -65135,7 +65163,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5041</v>
+        <v>5043</v>
       </c>
     </row>
   </sheetData>
